--- a/data/denuncias_clasificadas.xlsx
+++ b/data/denuncias_clasificadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
@@ -915,7 +915,7 @@
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1031,587 +1031,7 @@
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>'110016010000202522074'</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>'Ley 906</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>111</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1751158649000</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ESTAFA. ART. 246 C.P. MENOR CUANTIA</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>¿Qué viene a denunciar? ESTAFA ¿Cómo le pasó? Se comunica al Centro de Contacto de la Fiscalía General de la Nación el señor, HERMES JOSUE RODRIGUEZ MARIN con el fin de reportar los siguientes hechos Manifiesta lo siguiente: ¿El 13 de marzo del 2025 a las 13:56 horas realice una consignación por valor de 326.301 pesos, a una cuenta de Nequi sin embargo no cuento con el numero, pero se que se encuentra a Nombre Sura SA recaudo póliza Gustavo Lopez, y el numero de Referencia es M6259227. Deposite ese dinero debido a que ese mismo día estaba tratando de pagar el Soat de mi motocicleta, busque por medio de Google la pagina de SURA e ingrese a www.suraenlinea.com, cuando ingrese a la plataforma me solicitaron la placa, y salio todo el historial de la moto, luego me pidió el numero de documento y el nombre de la persona dueña de la moto, luego de eso me arrojo el botón de realizar pago, ingrese y me arrojo varios métodos de pago, ya que PSE estaba fuera de servicio, yo escogí la opción de nequi, allí ingrese mi numero y la clave dinámica, seguido de esto me arrojo que el pago había sido exitoso. sin embargo a mi correo no me llego ninguna confirmación. Luego el día 14 de marzo en la mañana, revise la pagina del Runt, pero no apariencia el seguro vigente, al ver esto me comunique con Sura a quienes les comente lo sucedido, ellos verificaron y me dijeron que no había ningún registro de pago, Adicional me informaron que habían suplantado la pagina de ellos y yo había sido victima de estafa, me recomendaron entonces realzar la denuncia. Posteriormente me comunique con Nequi, a quienes igualmente les comente lo sucedido, ellos me dijeron que el dinero que yo había depositado en dicha cuenta seguía allí, realizaron entonces un bloqueo temporal de la cuenta, y me dijeron que debía realizar la denuncia en fiscalía, y una vez realizada tenia que enviarles el numero de noticia criminal para que ellos me realizaran la devolución del dinero. Por el momento no cuento con mas información." Denuncia recibida en el centro de contacto por la agente Geraldine Paola Gómez.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>1737103950000</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Antioquia, MEDELLÍN - CARRERA 43 50 35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>VICTIMA</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>KAREN RANGEL GAVIRIA</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>'71387684'</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>jegarciao@unal.edu.co</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>BIENES MUEBLES</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>ACUERDO COMERCIAL</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>PERSONAL INMOBILIARIA</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>INDAGACION SIN PRESO P.A.</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>QUERELLABLE</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>QUERELLA</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>GMONTOYAM2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>'110016010000202521401'</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>'Ley 906</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>111</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1756737631000</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ESTAFA. ART. 246 C.P. MENOR CUANTIA</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>¿Qué viene a denunciar? ESTAFA ¿Cómo le pasó? El día 15 de abril de 2024 siendo las 5:30 pm aproximadamente, me encontraba caminando por el centro de Medellín, exactamente por Junín con Maracaibo, cuando fui abordada en la vía pública por un sujeto uniformado con camiseta de la empresa que me ofrecía beneficios y descuentos adquiriendo una membresía con una supuesta agencia de viajes llamada "Holding Pass S.A.S" y lo primero que preguntan es si cuento tarjeta de crédito, a lo que yo respondo que sí; al ingresar al establecimiento ubicado en la dirección Calle 53 # 47-60, encuentro que habían diferentes personas presentes a las que al parecer también les estaban asesorando y vendiendo paquetes y membresías de viajes; luego me brindan de tomar agua, a lo que accedo y bebo 2 vasos; posterior a esto me empiezan a asesorar sobre descuentos y facilidades en la forma de pago, yo le insistía al joven que me dijera inicialmente el costo de los viajes, a lo que él me evadía y seguía generando expectativa frente a la posibilidad de salir del país, luego de ofrecer empieza ese supuesto asesor a generar presión para que firme el contrato por un valor de $4´000.000 asociado a una membresía para poder viajar en cualquier momento en los siguientes 4 años; a lo que debido a la presión ejercida acepto e inmediatamente debitan de mi tarjeta de crédito ese monto; solicito pueda ser imputado su representante legal y a la vez sea devuelto el monto que se me fue debitado, ya que al momento de cotizar algún viaje con ellos, los precios incluso exceden los precios comerciales que uno como persona natural puede acceder.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>1742193608000</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Antioquia, MEDELLÍN - Calle 6 17 47, El Tesoro, Medellín, Antioquia, COL,ELTESORO</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>VICTIMA</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>CARLOS ANDRES PINEDA ZAPATA</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>'1152439707'</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>guinellavalero@gmail.com</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>OTROS</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ACUERDO COMERCIAL</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>MEDIOS DE COMUNICACIÓN Y REDES SOCIALES INTERNET</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>INDAGACION EN AVERIGUACION P.A.</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>QUERELLABLE</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>QUERELLA</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>PARODRIGUEZ</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>'050016000248202544053'</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>'Ley 906</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>111</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1750319778000</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ESTAFA. ART. 246 C.P. AGRAVADA CUANDO LA CONDUCTA ESTE RELACIONADA CON CONTRATOS DE SEGUROS O CON TRANSACCIONES SOBRE VEHICULOS AUTOMOTORES Art. 247 numeral 4 Adicionado por la Ley 1142 de 2007</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>¿Qué viene a denunciar? ESTAFA. ARTICULO 246. ¿Cómo le pasó? se logro contactar con una empresa y/o pesona que vende consolas de video y celulares. enviaron evidencias fotograficas de los productos y los costos adiconalmente envian camara y comercio , rut cedula e informacion del establecimiento luego de realizar la consignacion al numero de cuenta nequi 57 322 5141054 perteneciente al señor carlos tamayo por un valor de 500 mil pesos y suministrar los datos personales para el envio la entidad deja de responder al usuario bloquandolo de las redes y no volviendo a contestar</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>1748138462000</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Antioquia, MEDELLÍN - Medellín, Antioquia, COL,LOS ALCÁZARES</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>VICTIMA</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ANGEL ANTONIO PINO RENTERÍA</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>'43618117'</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>carolina050893@gmail.com</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>OFRECIMIENTO DE SERVICIOS</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>ACUERDO COMERCIAL</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>PERSONAL ENGAÑO EN VÍA PÚBLICA</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>INDAGACION EN AVERIGUACION P.A.</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>QUERELLABLE</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>DE OFICIO (INFORMES)</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>CSIERRAL1</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>'050016000248202544082'</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>'Ley 906</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>111</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1757612691000</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ESTAFA. ART. 246 C.P. MENOR CUANTIA</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>¿Qué viene a denunciar? ESTAFA ¿Cómo le pasó? A través de internet, di clic en un link de ¿SIMIT¿ para el pago de una fotomulta, este me lleva a la cuenta de Whasapp 3213039767, me enviaron el estado de cuenta y luego el total con el 50% de descuento; seguido me comparten los medios de pago que reciben ( varios bancos), una vez confirmado me pasa el QR de Bancolombia con el nombre ¿SIMIT¿ al cual procedo con el pago de 302027 pesos, seguidamente pido el paz y salvo y me dicen que debo pagar otros 83300 pesos, me comuniqué con movilidad en línea del municipio de Medellín y que eso era una estafa, igual respuesta me dieron al comunicarme con el SIMIT, del banco me piden hacer la denuncia para avanzar en la reclamación.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>1737516724000</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Antioquia, MEDELLÍN - Medellín, Antioquia, COL,CORAZÓN DE JESÚS</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>DENUNCIANTE</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ERIKA JANET MUNERA ANGEL</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>'43116866'</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>yesikamolinagil@gmail.com</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>OTROS</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>COMPRA</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>MEDIOS DE COMUNICACIÓN Y REDES SOCIALES CHATS</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>INDAGACION SIN PRESO P.A.</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>QUERELLABLE</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>QUERELLA</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>MACEVEDOS1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>'050016000248202544086'</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>'Ley 906</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>111</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1749664764000</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ESTAFA. ART. 246 C.P.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>¿Qué viene a denunciar? EXTORSIÓN ¿Cómo le pasó? Yo estaba en mi casa sola, recibí una llamada, en esta me dijeron que mi hija estaba detenida porque había provocado un accidente a una niña y que si no mandaba una plata la llevaban presa a la Fiscalía, primero me pidieron 1 millón, me dijeron que los consignará al numero de cuenta 91274629059 a nombre de Lina Cardona, yo bajé sola al centro comercial la central a mandar el dinero, ya me devolví a subir a mi casa pues me pidieron más plata, nunca me permitieron colgar, después me dijeron mandara 50 millones yo les dije que no tenia y me dijeron que buscara más plata en la casa, que ella o sea mi hija, tenía plata metida en las chaquetas o bolsos, que a mi hija la iban a llevar presa porque la niña había fallecido, logré reunir otro 1.500.000 y se los dije y me dijeron que si no tenia con quien buscar mas plata prestada y les dije que no tenía mas de donde.Bajé otra vez a la central y consigné el otro 1.500.000 a otra cuenta de NEQUI que me dieron para consignarla al número 3242941544, después de consignarlos me volvieron a decir que buscara los otros 50 millones y les dije que no tenía más.yo me volví a subir a mi casa, cuando tocan la puerta y era mi hija ahí mi hija me dijo que que paso que porque estaba tan pálida yo le contesté que ella por que no me había llamado cuando le conte ella cogio el teléfono habló y de una colgaron Cuando paso todo nos comunicamos con Bancolombia y nos dimos cuenta que fue una estafa, llamamos a Bancolombia y pusimos la queja y nos la recibieron con el radicado 8016693565 y nos dijeron que en esa cuenta aparecía esa consignación y que aún no la habían retirado También lo hicimos con nequi por el 1.500.000 y nos dieron el radicado 50511559 este nequi en el recibo que me dieron en el corresponsal aparece a nombre de Diego Cárdenas</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>1749613096000</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Antioquia, MEDELLÍN - </t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>VICTIMA</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>CRISTIAN CAMILO SALDARRIAGA CARUPIA</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>'1036688717'</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>georgedan51@hotmail.com</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>OFRECIMIENTO DE SERVICIOS</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>ACUERDO COMERCIAL</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>MEDIOS DE COMUNICACIÓN Y REDES SOCIALES FACEBOOK</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>INDAGACION EN AVERIGUACION P.A.</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>INDAGACIÓN</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>QUERELLA</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>MACEVEDOS1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/denuncias_clasificadas.xlsx
+++ b/data/denuncias_clasificadas.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
